--- a/outputs/explain_vs_predict_model_comparison.xlsx
+++ b/outputs/explain_vs_predict_model_comparison.xlsx
@@ -481,13 +481,13 @@
         <v>0.1314746766534546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.100654457113349</v>
+        <v>0.1006544571133491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1680184111420101</v>
+        <v>0.1680184111420099</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1081982630852669</v>
+        <v>0.1081982630852668</v>
       </c>
       <c r="H2" t="n">
         <v>-1600.406562199776</v>
